--- a/output/pdf_financials_xlsx/FHR.xlsx
+++ b/output/pdf_financials_xlsx/FHR.xlsx
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.054631</v>
+        <v>-0.054631</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.118396</v>
+        <v>-0.118396</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.032275</v>
+        <v>-0.032275</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-0.249129</v>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.054631</v>
+        <v>-0.054631</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.118396</v>
+        <v>-0.118396</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.032275</v>
+        <v>-0.032275</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.249129</v>
@@ -1004,13 +1004,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.054631</v>
+        <v>-0.054631</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.118396</v>
+        <v>-0.118396</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.032275</v>
+        <v>-0.032275</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-0.249129</v>
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.054631</v>
+        <v>-0.054631</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.118396</v>
+        <v>-0.118396</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.032275</v>
+        <v>-0.032275</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.249129</v>
@@ -1159,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>2.027475</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>4.550003</v>
       </c>
     </row>
     <row r="29">
@@ -1172,22 +1172,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.054631</v>
+        <v>-0.054631</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.118396</v>
+        <v>-0.118396</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.032275</v>
+        <v>-0.032275</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.249129</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-4.267219</v>
+        <v>-2.239744</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-6.650678</v>
+        <v>-2.100675</v>
       </c>
     </row>
     <row r="30">
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-119.8778247238485</v>
+        <v>-62.92052005258959</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-94.24599693738821</v>
+        <v>-29.76842505627967</v>
       </c>
     </row>
     <row r="31">
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.544013</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.581585</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.581585</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0.595014</v>
@@ -2959,10 +2959,10 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>2.027475</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>4.560913</v>
       </c>
     </row>
     <row r="101">
@@ -5570,7 +5570,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -5824,7 +5828,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -6100,7 +6108,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
         <v>0.544013</v>
       </c>
@@ -6328,7 +6340,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -9742,7 +9754,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -11213,13 +11225,13 @@
         </is>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.118396</v>
+        <v>-0.118396</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.032275</v>
+        <v>-0.032275</v>
       </c>
       <c r="H162" s="5" t="n">
-        <v>0.249129</v>
+        <v>-0.249129</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -11520,10 +11532,10 @@
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>0.054631</v>
+        <v>-0.054631</v>
       </c>
       <c r="F169" s="5" t="n">
-        <v>0.118396</v>
+        <v>-0.118396</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FHR.xlsx
+++ b/output/pdf_financials_xlsx/FHR.xlsx
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000309</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.054631</v>
+        <v>-0.054322</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.118396</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.054631</v>
+        <v>-0.054322</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.118396</v>
@@ -1295,22 +1295,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.050005</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.056054</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.029828</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.372153</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.699989</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.373862</v>
       </c>
     </row>
     <row r="35">
@@ -1345,22 +1345,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.050005</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.056054</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.029828</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.372153</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.699989</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.373862</v>
       </c>
     </row>
     <row r="37">
@@ -1645,22 +1645,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.050005</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.056054</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.029828</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.372153</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.797807</v>
+        <v>0.097818</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.772545</v>
+        <v>0.398683</v>
       </c>
     </row>
     <row r="49">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">

--- a/output/pdf_financials_xlsx/FHR.xlsx
+++ b/output/pdf_financials_xlsx/FHR.xlsx
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.108406</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.098568</v>
       </c>
     </row>
     <row r="71">
@@ -2244,10 +2244,10 @@
         <v>0</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>12.168017</v>
+        <v>12.276423</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>12.242089</v>
+        <v>12.340657</v>
       </c>
     </row>
     <row r="72">
@@ -2344,10 +2344,10 @@
         <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1.358406</v>
+        <v>1.25</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>1.7949</v>
+        <v>1.696332</v>
       </c>
     </row>
     <row r="76">
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2.059290666068241</v>
+        <v>2.077637078959166</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>210.4862192878389</v>
+        <v>212.1809631883908</v>
       </c>
     </row>
     <row r="81">
@@ -3536,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G123" s="3" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>-0.4</v>
@@ -4498,7 +4498,11 @@
           <t>Current portion of lease obligations 11</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -7266,7 +7270,11 @@
           <t>Increase in long-term debt 12</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -8288,7 +8296,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
